--- a/data/admins.xlsx
+++ b/data/admins.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$eS.FMIYwRsh5b60VYmzNeQ$uHGUP2EV7fsv5JV1xCcan7ewoqpP/0z8tofALPGhK2Q</t>
+          <t>$pbkdf2-sha256$29000$M8aYcw5hLOX8/3.vVcq51w$XP9JFGHs95/fAjAeBIgcegujHaPKjXL7NR4KLsto3Qs</t>
         </is>
       </c>
     </row>
@@ -505,34 +505,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$OeecMyZECEFICSEEIETI2Q$uq6Ny7jG.ZZXlYiThAo2123rS4BZhkBlGOLuNridyE4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3bea299c</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>id23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>shreyas p</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4mh23cs147@gmail.com</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>$pbkdf2-sha256$29000$RGgtpdRa653z3tsbw9j7/w$JHjB4Xo4CeeFLH/kYjIj2Paa16AsuOS221kRHLmnPHE</t>
+          <t>$pbkdf2-sha256$29000$ZAyBMEbonRMC4BxDiPH.nw$IZ7fygpfQJ4595cbC0g7lYUPiP7ntFBWATOPGf9gwok</t>
         </is>
       </c>
     </row>
